--- a/data/trans_camb/IP43-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP43-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,44</t>
+          <t>-11,98; 2,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,89; -14,34</t>
+          <t>-24,97; -14,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 1,03</t>
+          <t>-14,63; 1,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,61; -17,32</t>
+          <t>-29,41; -17,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -0,46</t>
+          <t>-11,35; -1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,37; -17,34</t>
+          <t>-25,08; -17,37</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 16,65</t>
+          <t>-51,43; 13,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 5,88</t>
+          <t>-57,18; 5,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,56; -2,62</t>
+          <t>-47,96; -5,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -5,31</t>
+          <t>-16,52; -5,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -19,17</t>
+          <t>-28,34; -19,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,97; -8,41</t>
+          <t>-19,69; -8,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -19,51</t>
+          <t>-27,92; -19,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -8,98</t>
+          <t>-16,38; -8,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,28; -21,13</t>
+          <t>-27,13; -20,91</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,53; -25,1</t>
+          <t>-60,94; -22,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,43; -39,0</t>
+          <t>-71,96; -39,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,33; -40,55</t>
+          <t>-63,15; -40,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,04; -9,83</t>
+          <t>-23,97; -10,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,36; -20,42</t>
+          <t>-32,47; -21,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,37; -7,95</t>
+          <t>-20,81; -8,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -18,46</t>
+          <t>-29,37; -18,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,28; -10,93</t>
+          <t>-19,84; -10,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,21; -21,31</t>
+          <t>-29,24; -21,27</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,21; -44,73</t>
+          <t>-76,69; -46,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,04; -39,1</t>
+          <t>-73,87; -38,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,44; -49,74</t>
+          <t>-72,28; -49,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -1,39</t>
+          <t>-14,56; -1,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -16,97</t>
+          <t>-27,29; -17,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; -3,21</t>
+          <t>-16,44; -3,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,65; -18,01</t>
+          <t>-28,82; -18,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -4,49</t>
+          <t>-13,98; -4,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -18,77</t>
+          <t>-26,02; -18,9</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,75; -2,88</t>
+          <t>-58,44; -7,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,49; -14,79</t>
+          <t>-62,55; -15,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,91; -24,1</t>
+          <t>-55,67; -21,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -7,09</t>
+          <t>-14,03; -7,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,82; -20,59</t>
+          <t>-25,51; -20,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -8,97</t>
+          <t>-15,34; -8,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-26,06; -20,77</t>
+          <t>-25,83; -20,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -8,86</t>
+          <t>-13,29; -8,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -21,13</t>
+          <t>-24,95; -21,47</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -34,58</t>
+          <t>-56,01; -34,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -41,59</t>
+          <t>-60,1; -40,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,23; -40,91</t>
+          <t>-55,25; -40,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
